--- a/Test Data/API_Data.xlsx
+++ b/Test Data/API_Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29926"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Testing\Downloads\API_Automation_Friday_PPT (2)\API_Automation_Friday_PPT\API_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Testing\API_Automation_UiPath\Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">{_x000d_
     "firstName": "Satiksha",_x000d_
     "lastName": "Choudhary",_x000d_
-    "email": "satiksha123@gmail.com",_x000d_
+    "email": "satiksha1234@gmail.com",_x000d_
     "password": "12345678"_x000d_
 }</t>
   </si>
@@ -504,7 +504,6 @@
       <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="I3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
